--- a/Outputs/Data/stanoviste/mzchu_25_biotopy_druhy_20260217.xlsx
+++ b/Outputs/Data/stanoviste/mzchu_25_biotopy_druhy_20260217.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">SITECODE</t>
   </si>
@@ -77,6 +77,9 @@
     <t xml:space="preserve">INVASIVE</t>
   </si>
   <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXPANSIVE</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t xml:space="preserve">INVASIVE_LIST</t>
   </si>
   <si>
+    <t xml:space="preserve">Arctium lappa, Armoracia rusticana, Arrhenatherum elatius, Artemisia absinthium, Atriplex patula, Berteroa incana, Bromus tectorum, Capsella bursa-pastoris, Conyza canadensis, Descurainia sophia, Digitaria sanguinalis, Erodium cicutarium, Erysimum cheiranthoides, Geranium pusillum, Lactuca serriola, Lamium album, Lamium purpureum, Medicago ×varia, Medicago sativa, Melilotus albus, Oenothera biennis, Papaver dubium, Prunus domestica, Quercus rubra, Robinia pseudoacacia, Rumex thyrsiflorus, Saponaria officinalis, Setaria pumila, Silene latifolia subsp. alba, Silene noctiflora, Solidago canadensis, Symphoricarpos albus, Veronica arvensis, Veronica triphyllos, Vicia angustifolia</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXPANSIVE_LIST</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t xml:space="preserve">Cypripedium calceolus</t>
   </si>
   <si>
+    <t xml:space="preserve">Robinia pseudoacacia, Aesculus hippocastanum, Ailanthus altissima, Arctium lappa, Arctium tomentosum, Arrhenatherum elatius, Asparagus officinalis, Atriplex oblongifolia, Carduus acanthoides, Cichorium intybus, Cirsium arvense, Convolvulus arvensis, Echinops sphaerocephalus, Fumaria officinalis, Chenopodium bonus-henricus, Juglans regia, Lamium album, Melilotus officinalis, Onobrychis viciifolia, Pinus nigra, Pyrus communis, Quercus rubra, Reseda lutea, Reseda luteola, Silene latifolia subsp. alba, Sisymbrium officinale, Tragopogon dubius</t>
+  </si>
+  <si>
     <t xml:space="preserve">L6.4</t>
   </si>
   <si>
@@ -122,6 +131,9 @@
     <t xml:space="preserve">0.3708</t>
   </si>
   <si>
+    <t xml:space="preserve">Echinops sphaerocephalus, Robinia pseudoacacia</t>
+  </si>
+  <si>
     <t xml:space="preserve">T3.3D</t>
   </si>
   <si>
@@ -143,6 +155,18 @@
     <t xml:space="preserve">0.3891</t>
   </si>
   <si>
+    <t xml:space="preserve">60.5844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robinia pseudoacacia, Arrhenatherum elatius, Asparagus officinalis, Onobrychis viciifolia, Pinus nigra, Convolvulus arvensis, Pyrus communis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betula pendula, Bromus erectus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Třtěnské stráně</t>
   </si>
   <si>
@@ -155,12 +179,27 @@
     <t xml:space="preserve">1.3168</t>
   </si>
   <si>
+    <t xml:space="preserve">99.6892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melampyrum arvense, Onobrychis viciifolia, Reseda lutea, Colutea arborescens, Sonchus arvensis, Symphoricarpos albus, Adonis aestivalis, Cameraria ohridella, Caucalis platycarpos subsp. platycarpos, Cirsium arvense, Convolvulus arvensis, Euphorbia falcata, Pinus nigra, Robinia pseudoacacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phragmites australis</t>
+  </si>
+  <si>
     <t xml:space="preserve">T7</t>
   </si>
   <si>
     <t xml:space="preserve">0.2891</t>
   </si>
   <si>
+    <t xml:space="preserve">Adonis aestivalis, Cameraria ohridella, Caucalis platycarpos subsp. platycarpos, Cirsium arvense, Colutea arborescens, Convolvulus arvensis, Euphorbia falcata, Melampyrum arvense, Onobrychis viciifolia, Pinus nigra, Reseda lutea, Robinia pseudoacacia, Symphoricarpos albus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hodonínská Dúbrava</t>
   </si>
   <si>
@@ -188,9 +227,21 @@
     <t xml:space="preserve">0.3287</t>
   </si>
   <si>
+    <t xml:space="preserve">88.4563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.489</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gladiolus palustris</t>
   </si>
   <si>
+    <t xml:space="preserve">Impatiens parviflora, Parthenocissus inserta, Solidago gigantea, Acer negundo, Prunus serotina, Robinia pseudoacacia, Symphyotrichum lanceolatum, Mahonia aquifolium, Cirsium arvense, Erechtites hieraciifolius, Arctium lappa, Juglans regia, Malus domestica, Bidens frondosa, Erigeron annuus, Oxalis stricta, Populus ×canadensis, Quercus rubra, Tanacetum vulgare, Arrhenatherum elatius, Convolvulus arvensis, Pyrus communis, Ribes rubrum, Asparagus officinalis, Carduus acanthoides, Conyza canadensis, Lactuca serriola, Linaria vulgaris, Saponaria officinalis, Silene latifolia subsp. alba, Digitaria sanguinalis, Juncus tenuis, Tragopogon dubius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alnus glutinosa, Salix alba, Phragmites australis, Betula pendula, Brachypodium sylvaticum, Carex acutiformis, Rubus caesius, Salix cinerea, Pinus sylvestris, Tilia cordata</t>
+  </si>
+  <si>
     <t xml:space="preserve">L3.4</t>
   </si>
   <si>
@@ -212,6 +263,18 @@
     <t xml:space="preserve">0.2978</t>
   </si>
   <si>
+    <t xml:space="preserve">83.3593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impatiens parviflora, Prunus serotina, Solidago gigantea, Ailanthus altissima, Arrhenatherum elatius, Conyza canadensis, Pinus nigra, Robinia pseudoacacia, Symphyotrichum lanceolatum, Viola odorata, Asparagus officinalis, Bromus sterilis, Erigeron annuus, Linaria vulgaris, Oxalis stricta, Setaria pumila, Tanacetum vulgare, Tragopogon dubius, Acer negundo, Arctium lappa, Geranium pusillum, Parthenocissus inserta, Bidens frondosa, Digitaria sanguinalis, Duchesnea indica, Juncus tenuis, Quercus rubra, Nepeta cataria, Pyrus communis, Saponaria officinalis, Vinca minor, Galinsoga parviflora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tilia cordata, Dactylis glomerata, Aegopodium podagraria, Frangula alnus</t>
+  </si>
+  <si>
     <t xml:space="preserve">L6.3</t>
   </si>
   <si>
@@ -231,6 +294,18 @@
   </si>
   <si>
     <t xml:space="preserve">0.2616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrhenatherum elatius, Impatiens parviflora, Prunus serotina, Robinia pseudoacacia, Ailanthus altissima, Erechtites hieraciifolius, Oxalis stricta, Quercus rubra, Silene latifolia subsp. alba, Solidago gigantea, Symphyotrichum lanceolatum, Asparagus officinalis, Conyza canadensis, Viola odorata, Linaria vulgaris, Juglans regia, Saponaria officinalis, Symphoricarpos albus, Erigeron annuus, Melilotus officinalis, Setaria pumila, Sonchus oleraceus, Cirsium arvense, Parthenocissus inserta, Thlaspi arvense, Echinochloa crus-galli, Chenopodium strictum, Juncus tenuis, Lepidium campestre, Tanacetum vulgare, Bromus tectorum, Convolvulus arvensis, Lathyrus tuberosus, Sonchus arvensis, Veronica arvensis, Arctium lappa, Digitaria ischaemum, Sambucus ebulus, Acer negundo, Anthriscus caucalis, Lactuca serriola, Lamium purpureum, Malus domestica, Pinus nigra, Pseudotsuga menziesii, Solidago canadensis, Bidens frondosa, Erysimum cheiranthoides, Carduus acanthoides, Capsella bursa-pastoris, Erodium cicutarium, Sonchus asper, Bromus sterilis, Tragopogon dubius, Populus ×canadensis, Sorbus domestica, Ambrosia artemisiifolia, Crepis setosa, Mahonia aquifolium, Pyrus communis, Vicia angustifolia, Dysphania pumilio, Epilobium adenocaulon, Fumaria vaillantii, Rumex thyrsiflorus, Digitaria sanguinalis, Oxalis dillenii, Ribes rubrum, Senecio vulgaris, Tripleurospermum inodorum, Vicia sativa, Harmonia axyridis, Lysimachia punctata, Myocastor coypus, Galinsoga parviflora, Helianthus tuberosus, Lamium album, Viola ×scabra, Viola suavis, Atriplex patula, Vinca minor, Aesculus hippocastanum, Armoracia rusticana, Berteroa incana, Lepidium virginicum, Melissa officinalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinus sylvestris, Tilia cordata, Betula pendula, Agrostis capillaris, Calamagrostis epigejos, Brachypodium sylvaticum, Melica uniflora, Dactylis glomerata, Fallopia dumetorum, Chelidonium majus, Rubus caesius, Populus tremula, Lysimachia vulgaris, Carex acutiformis, Frangula alnus, Phragmites australis, Ligustrum vulgare, Alnus glutinosa</t>
   </si>
   <si>
     <t xml:space="preserve">V2</t>
@@ -739,7 +814,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -759,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -782,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10"/>
     </row>
@@ -803,9 +878,11 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11"/>
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -824,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G12"/>
     </row>
@@ -833,10 +910,10 @@
         <v>1183</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -852,10 +929,10 @@
         <v>1183</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -869,10 +946,10 @@
         <v>1183</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -886,10 +963,10 @@
         <v>1183</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -903,10 +980,10 @@
         <v>1183</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -920,10 +997,10 @@
         <v>1183</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -937,10 +1014,10 @@
         <v>1183</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -954,15 +1031,15 @@
         <v>1183</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20"/>
     </row>
@@ -971,15 +1048,15 @@
         <v>1183</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G21"/>
     </row>
@@ -988,15 +1065,15 @@
         <v>1183</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G22"/>
     </row>
@@ -1005,15 +1082,15 @@
         <v>1183</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G23"/>
     </row>
@@ -1022,22 +1099,22 @@
         <v>1183</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1045,16 +1122,16 @@
         <v>1183</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -1068,16 +1145,16 @@
         <v>1183</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -1091,22 +1168,22 @@
         <v>1183</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1114,16 +1191,16 @@
         <v>1183</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>17</v>
@@ -1137,22 +1214,22 @@
         <v>1183</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -1160,22 +1237,22 @@
         <v>1183</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -1183,19 +1260,19 @@
         <v>1183</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" t="s">
         <v>19</v>
@@ -1206,22 +1283,22 @@
         <v>1183</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -1229,40 +1306,42 @@
         <v>1183</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33"/>
+        <v>24</v>
+      </c>
+      <c r="G33" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>1183</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G34"/>
     </row>
@@ -1271,22 +1350,22 @@
         <v>1183</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
@@ -1294,16 +1373,16 @@
         <v>1183</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -1317,16 +1396,16 @@
         <v>1183</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -1340,16 +1419,16 @@
         <v>1183</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -1363,16 +1442,16 @@
         <v>1183</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>17</v>
@@ -1386,22 +1465,22 @@
         <v>1183</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -1409,22 +1488,22 @@
         <v>1183</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
@@ -1432,19 +1511,19 @@
         <v>1183</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
@@ -1455,22 +1534,22 @@
         <v>1183</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
@@ -1478,40 +1557,42 @@
         <v>1183</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
-      </c>
-      <c r="G44"/>
+        <v>24</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>1183</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G45"/>
     </row>
@@ -1520,10 +1601,10 @@
         <v>1183</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D46"/>
       <c r="E46"/>
@@ -1539,10 +1620,10 @@
         <v>1183</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D47"/>
       <c r="E47"/>
@@ -1556,10 +1637,10 @@
         <v>1183</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
@@ -1573,10 +1654,10 @@
         <v>1183</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D49"/>
       <c r="E49"/>
@@ -1590,10 +1671,10 @@
         <v>1183</v>
       </c>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D50"/>
       <c r="E50"/>
@@ -1607,10 +1688,10 @@
         <v>1183</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D51"/>
       <c r="E51"/>
@@ -1624,10 +1705,10 @@
         <v>1183</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D52"/>
       <c r="E52"/>
@@ -1641,15 +1722,15 @@
         <v>1183</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D53"/>
       <c r="E53"/>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G53"/>
     </row>
@@ -1658,15 +1739,15 @@
         <v>1183</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G54"/>
     </row>
@@ -1675,15 +1756,15 @@
         <v>1183</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G55"/>
     </row>
@@ -1692,15 +1773,15 @@
         <v>1183</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G56"/>
     </row>
@@ -1709,22 +1790,22 @@
         <v>1183</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F57" t="s">
         <v>10</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
@@ -1732,22 +1813,22 @@
         <v>1183</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -1755,22 +1836,22 @@
         <v>1183</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
@@ -1778,16 +1859,16 @@
         <v>1183</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -1799,16 +1880,16 @@
         <v>1183</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
@@ -1820,22 +1901,22 @@
         <v>1183</v>
       </c>
       <c r="B62" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s">
         <v>18</v>
       </c>
       <c r="G62" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
@@ -1843,22 +1924,22 @@
         <v>1183</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D63" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s">
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64">
@@ -1866,22 +1947,22 @@
         <v>1183</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D64" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
@@ -1889,22 +1970,22 @@
         <v>1183</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66">
@@ -1912,64 +1993,68 @@
         <v>1183</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F66" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66"/>
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>1183</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
-      </c>
-      <c r="G67"/>
+        <v>26</v>
+      </c>
+      <c r="G67" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>2213</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F68" t="s">
         <v>10</v>
       </c>
       <c r="G68" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69">
@@ -1977,22 +2062,22 @@
         <v>2213</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E69" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70">
@@ -2000,22 +2085,22 @@
         <v>2213</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E70" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71">
@@ -2023,16 +2108,16 @@
         <v>2213</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C71" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E71" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -2044,16 +2129,16 @@
         <v>2213</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F72" t="s">
         <v>17</v>
@@ -2065,16 +2150,16 @@
         <v>2213</v>
       </c>
       <c r="B73" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C73" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E73" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -2088,22 +2173,22 @@
         <v>2213</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E74" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F74" t="s">
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -2111,22 +2196,22 @@
         <v>2213</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C75" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E75" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G75" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76">
@@ -2134,19 +2219,19 @@
         <v>2213</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D76" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G76"/>
     </row>
@@ -2155,64 +2240,68 @@
         <v>2213</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C77" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E77" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
-      </c>
-      <c r="G77"/>
+        <v>24</v>
+      </c>
+      <c r="G77" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>2213</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
-      </c>
-      <c r="G78"/>
+        <v>26</v>
+      </c>
+      <c r="G78" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>2213</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E79" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F79" t="s">
         <v>10</v>
       </c>
       <c r="G79" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -2220,16 +2309,16 @@
         <v>2213</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C80" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D80" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -2243,16 +2332,16 @@
         <v>2213</v>
       </c>
       <c r="B81" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D81" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
@@ -2266,16 +2355,16 @@
         <v>2213</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
@@ -2287,16 +2376,16 @@
         <v>2213</v>
       </c>
       <c r="B83" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
@@ -2308,16 +2397,16 @@
         <v>2213</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -2331,22 +2420,22 @@
         <v>2213</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F85" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
@@ -2354,22 +2443,22 @@
         <v>2213</v>
       </c>
       <c r="B86" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E86" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F86" t="s">
+        <v>22</v>
+      </c>
+      <c r="G86" t="s">
         <v>21</v>
-      </c>
-      <c r="G86" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="87">
@@ -2377,19 +2466,19 @@
         <v>2213</v>
       </c>
       <c r="B87" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C87" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D87" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G87"/>
     </row>
@@ -2398,64 +2487,68 @@
         <v>2213</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C88" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F88" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88"/>
+        <v>24</v>
+      </c>
+      <c r="G88" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
         <v>2213</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C89" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
-      </c>
-      <c r="G89"/>
+        <v>26</v>
+      </c>
+      <c r="G89" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
         <v>5874</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E90" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F90" t="s">
         <v>10</v>
       </c>
       <c r="G90" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91">
@@ -2463,22 +2556,22 @@
         <v>5874</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C91" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D91" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E91" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
       </c>
       <c r="G91" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92">
@@ -2486,22 +2579,22 @@
         <v>5874</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E92" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93">
@@ -2509,22 +2602,22 @@
         <v>5874</v>
       </c>
       <c r="B93" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C93" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D93" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E93" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94">
@@ -2532,16 +2625,16 @@
         <v>5874</v>
       </c>
       <c r="B94" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D94" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E94" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F94" t="s">
         <v>17</v>
@@ -2555,22 +2648,22 @@
         <v>5874</v>
       </c>
       <c r="B95" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C95" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D95" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E95" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F95" t="s">
         <v>18</v>
       </c>
       <c r="G95" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96">
@@ -2578,22 +2671,22 @@
         <v>5874</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C96" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D96" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E96" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F96" t="s">
         <v>20</v>
       </c>
       <c r="G96" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97">
@@ -2601,22 +2694,22 @@
         <v>5874</v>
       </c>
       <c r="B97" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C97" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D97" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E97" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G97" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98">
@@ -2624,22 +2717,22 @@
         <v>5874</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C98" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D98" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G98" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99">
@@ -2647,64 +2740,68 @@
         <v>5874</v>
       </c>
       <c r="B99" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D99" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E99" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
-      </c>
-      <c r="G99"/>
+        <v>24</v>
+      </c>
+      <c r="G99" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>5874</v>
       </c>
       <c r="B100" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C100" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D100" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E100" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
-      </c>
-      <c r="G100"/>
+        <v>26</v>
+      </c>
+      <c r="G100" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>5874</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C101" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D101" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F101" t="s">
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102">
@@ -2712,22 +2809,22 @@
         <v>5874</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C102" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D102" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E102" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103">
@@ -2735,22 +2832,22 @@
         <v>5874</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C103" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D103" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F103" t="s">
         <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104">
@@ -2758,22 +2855,22 @@
         <v>5874</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D104" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F104" t="s">
         <v>16</v>
       </c>
       <c r="G104" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105">
@@ -2781,16 +2878,16 @@
         <v>5874</v>
       </c>
       <c r="B105" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D105" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E105" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F105" t="s">
         <v>17</v>
@@ -2804,22 +2901,22 @@
         <v>5874</v>
       </c>
       <c r="B106" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D106" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E106" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F106" t="s">
         <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107">
@@ -2827,22 +2924,22 @@
         <v>5874</v>
       </c>
       <c r="B107" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C107" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E107" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
     </row>
     <row r="108">
@@ -2850,22 +2947,22 @@
         <v>5874</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D108" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E108" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G108" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109">
@@ -2873,22 +2970,22 @@
         <v>5874</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C109" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D109" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E109" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F109" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G109" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110">
@@ -2896,64 +2993,68 @@
         <v>5874</v>
       </c>
       <c r="B110" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C110" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E110" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F110" t="s">
-        <v>23</v>
-      </c>
-      <c r="G110"/>
+        <v>24</v>
+      </c>
+      <c r="G110" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>5874</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D111" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E111" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F111" t="s">
-        <v>24</v>
-      </c>
-      <c r="G111"/>
+        <v>26</v>
+      </c>
+      <c r="G111" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>5874</v>
       </c>
       <c r="B112" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D112" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E112" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F112" t="s">
         <v>10</v>
       </c>
       <c r="G112" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="113">
@@ -2961,22 +3062,22 @@
         <v>5874</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D113" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E113" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F113" t="s">
         <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="114">
@@ -2984,22 +3085,22 @@
         <v>5874</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C114" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D114" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E114" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115">
@@ -3007,22 +3108,22 @@
         <v>5874</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C115" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D115" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E115" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F115" t="s">
         <v>16</v>
       </c>
       <c r="G115" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116">
@@ -3030,16 +3131,16 @@
         <v>5874</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C116" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D116" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E116" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F116" t="s">
         <v>17</v>
@@ -3053,22 +3154,22 @@
         <v>5874</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C117" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D117" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E117" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F117" t="s">
         <v>18</v>
       </c>
       <c r="G117" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="118">
@@ -3076,22 +3177,22 @@
         <v>5874</v>
       </c>
       <c r="B118" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C118" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D118" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E118" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F118" t="s">
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119">
@@ -3099,22 +3200,22 @@
         <v>5874</v>
       </c>
       <c r="B119" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D119" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E119" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F119" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G119" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="120">
@@ -3122,22 +3223,22 @@
         <v>5874</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C120" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D120" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E120" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F120" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121">
@@ -3145,52 +3246,56 @@
         <v>5874</v>
       </c>
       <c r="B121" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C121" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D121" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E121" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F121" t="s">
-        <v>23</v>
-      </c>
-      <c r="G121"/>
+        <v>24</v>
+      </c>
+      <c r="G121" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>5874</v>
       </c>
       <c r="B122" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C122" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D122" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E122" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F122" t="s">
-        <v>24</v>
-      </c>
-      <c r="G122"/>
+        <v>26</v>
+      </c>
+      <c r="G122" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>5874</v>
       </c>
       <c r="B123" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D123"/>
       <c r="E123"/>
@@ -3206,10 +3311,10 @@
         <v>5874</v>
       </c>
       <c r="B124" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D124"/>
       <c r="E124"/>
@@ -3223,10 +3328,10 @@
         <v>5874</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C125" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D125"/>
       <c r="E125"/>
@@ -3240,10 +3345,10 @@
         <v>5874</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C126" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D126"/>
       <c r="E126"/>
@@ -3257,10 +3362,10 @@
         <v>5874</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C127" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D127"/>
       <c r="E127"/>
@@ -3274,10 +3379,10 @@
         <v>5874</v>
       </c>
       <c r="B128" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C128" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D128"/>
       <c r="E128"/>
@@ -3291,10 +3396,10 @@
         <v>5874</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C129" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D129"/>
       <c r="E129"/>
@@ -3308,15 +3413,15 @@
         <v>5874</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C130" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D130"/>
       <c r="E130"/>
       <c r="F130" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G130"/>
     </row>
@@ -3325,15 +3430,15 @@
         <v>5874</v>
       </c>
       <c r="B131" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C131" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D131"/>
       <c r="E131"/>
       <c r="F131" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G131"/>
     </row>
@@ -3342,15 +3447,15 @@
         <v>5874</v>
       </c>
       <c r="B132" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C132" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D132"/>
       <c r="E132"/>
       <c r="F132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G132"/>
     </row>
@@ -3359,15 +3464,15 @@
         <v>5874</v>
       </c>
       <c r="B133" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C133" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D133"/>
       <c r="E133"/>
       <c r="F133" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G133"/>
     </row>
